--- a/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -2,16</t>
+          <t>-10,98; -1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,25</t>
+          <t>-5,19; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,01</t>
+          <t>-5,15; 3,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,47</t>
+          <t>-4,01; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,62</t>
+          <t>-0,53; 5,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,62</t>
+          <t>-2,1; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,61</t>
+          <t>-3,34; 1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,2</t>
+          <t>-4,05; 1,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,0</t>
+          <t>-5,4; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,63</t>
+          <t>-1,84; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,32</t>
+          <t>-1,32; 4,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,36</t>
+          <t>-3,2; 4,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,29</t>
+          <t>-1,85; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,24</t>
+          <t>1,43; 11,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 4,67</t>
+          <t>-2,99; 4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,41</t>
+          <t>-6,18; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,0</t>
+          <t>-11,16; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 8,43</t>
+          <t>-3,85; 8,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,0</t>
+          <t>-7,56; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,21</t>
+          <t>-2,18; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,62</t>
+          <t>-2,02; 1,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,23</t>
+          <t>-2,3; 3,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,2</t>
+          <t>-1,04; 5,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,65</t>
+          <t>-0,61; 3,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,46</t>
+          <t>-1,56; 3,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,68</t>
+          <t>-2,18; 0,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,0</t>
+          <t>-2,99; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,26; —</t>
+          <t>-82,06; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 734,05</t>
+          <t>-76,55; 514,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,11</t>
+          <t>-0,83; 1,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,66</t>
+          <t>-0,87; 1,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1475,27 +1475,27 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,63</t>
+          <t>-0,44; 1,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 160,18</t>
+          <t>-52,87; 153,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 152,11</t>
+          <t>-39,04; 140,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 155,35</t>
+          <t>-65,23; 153,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 272,34</t>
+          <t>-36,87; 277,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -1,16</t>
+          <t>-10,85; -1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,26</t>
+          <t>-5,18; 4,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,09</t>
+          <t>-4,83; 2,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,34</t>
+          <t>-4,17; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,68</t>
+          <t>-0,54; 5,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,46</t>
+          <t>-2,5; 4,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,22</t>
+          <t>-3,37; 1,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,21</t>
+          <t>-3,24; 1,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 0,0</t>
+          <t>-6,29; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,32</t>
+          <t>-1,82; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,59</t>
+          <t>-1,39; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,12</t>
+          <t>-3,97; 4,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,25</t>
+          <t>-1,85; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 11,93</t>
+          <t>1,37; 12,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,63</t>
+          <t>-2,99; 4,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,55</t>
+          <t>-6,08; 4,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 0,0</t>
+          <t>-11,71; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 8,13</t>
+          <t>-3,66; 8,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,0</t>
+          <t>-7,78; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,22</t>
+          <t>-2,4; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,16</t>
+          <t>-1,98; 1,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,07</t>
+          <t>-2,23; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,28</t>
+          <t>-0,9; 5,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 640,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,73</t>
+          <t>-0,68; 3,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,42</t>
+          <t>-1,53; 3,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,69</t>
+          <t>-2,21; 0,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,0</t>
+          <t>-2,96; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,06; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 514,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,12</t>
+          <t>-0,91; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,59</t>
+          <t>-0,84; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,84</t>
+          <t>-0,86; 0,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,63</t>
+          <t>-0,49; 1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 153,6</t>
+          <t>-51,47; 155,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 140,6</t>
+          <t>-38,12; 140,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 153,28</t>
+          <t>-62,57; 157,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 277,45</t>
+          <t>-42,76; 295,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,77%</t>
+          <t>-20,98%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -1,17</t>
+          <t>-11,88; -2,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,66</t>
+          <t>-5,07; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,9</t>
+          <t>-4,8; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,24</t>
+          <t>-4,93; 3,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-27,7%</t>
+          <t>-10,67%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,42</t>
+          <t>-0,53; 5,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,09</t>
+          <t>-2,5; 3,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,09</t>
+          <t>-4,02; 0,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,38</t>
+          <t>-2,72; 1,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,0</t>
+          <t>-6,3; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 7,42</t>
+          <t>-1,82; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,08</t>
+          <t>-1,44; 4,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 4,27</t>
+          <t>-3,3; 4,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,22</t>
+          <t>-1,87; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,31</t>
+          <t>1,48; 13,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,77</t>
+          <t>-2,98; 4,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,58</t>
+          <t>-6,1; 4,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 0,0</t>
+          <t>-10,07; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,3</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 8,28</t>
+          <t>-3,78; 8,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,0</t>
+          <t>-6,64; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>133,5%</t>
+          <t>141,12%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,21</t>
+          <t>-2,68; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,61</t>
+          <t>-1,97; 1,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,84</t>
+          <t>-2,16; 3,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,41</t>
+          <t>-1,09; 5,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 640,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,51</t>
+          <t>-0,54; 3,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,55</t>
+          <t>-1,52; 3,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,38</t>
+          <t>-2,23; 0,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-67,26; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,14; 734,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,06</t>
+          <t>-0,92; 1,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,51</t>
+          <t>-0,87; 1,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,85</t>
+          <t>-0,95; 0,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,62</t>
+          <t>-0,41; 1,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 155,31</t>
+          <t>-55,44; 160,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 140,67</t>
+          <t>-41,17; 152,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 157,67</t>
+          <t>-64,61; 155,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 295,71</t>
+          <t>-37,23; 326,61</t>
         </is>
       </c>
     </row>
